--- a/outputs/40959.xlsx
+++ b/outputs/40959.xlsx
@@ -144,24 +144,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -357,78 +361,78 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="str">
-        <f aca="false">IF(A2="","",IF(AND(A2="Sales",B2=""),"Sales","Marketing"))</f>
+      <c r="C2" s="1" t="str">
+        <f aca="false">IF(AND(A2="Sales",B2=""),"Sales","Marketing")</f>
         <v>Sales</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false">IF(A3="","",IF(AND(A3="Sales",B3=""),"Sales","Marketing"))</f>
+      <c r="C3" s="1" t="str">
+        <f aca="false">IF(AND(A3="Sales",B3=""),"Sales","Marketing")</f>
         <v>Marketing</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false">IF(A4="","",IF(AND(A4="Sales",B4=""),"Sales","Marketing"))</f>
+      <c r="C4" s="1" t="str">
+        <f aca="false">IF(AND(A4="Sales",B4=""),"Sales","Marketing")</f>
         <v>Marketing</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="str">
-        <f aca="false">IF(A5="","",IF(AND(A5="Sales",B5=""),"Sales","Marketing"))</f>
+      <c r="C5" s="1" t="str">
+        <f aca="false">IF(AND(A5="Sales",B5=""),"Sales","Marketing")</f>
         <v>Marketing</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="str">
-        <f aca="false">IF(A6="","",IF(AND(A6="Sales",B6=""),"Sales","Marketing"))</f>
+      <c r="C6" s="5" t="str">
+        <f aca="false">IF(AND(A6="Sales",B6=""),"Sales","Marketing")</f>
         <v>Marketing</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="0" t="str">
-        <f aca="false">IF(A7="","",IF(AND(A7="Sales",B7=""),"Sales","Marketing"))</f>
+      <c r="C7" s="1" t="str">
+        <f aca="false">IF(AND(A7="Sales",B7=""),"Sales","Marketing")</f>
         <v>Sales</v>
       </c>
     </row>

--- a/outputs/40959.xlsx
+++ b/outputs/40959.xlsx
@@ -383,7 +383,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f aca="false">IF(AND(A2="Sales",B2=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A2="Sales",B2="General"),"Marketing",IF(A2="Sales","Sales","Marketing"))</f>
         <v>Sales</v>
       </c>
     </row>
@@ -392,7 +392,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="str">
-        <f aca="false">IF(AND(A3="Sales",B3=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A3="Sales",B3="General"),"Marketing",IF(A3="Sales","Sales","Marketing"))</f>
         <v>Marketing</v>
       </c>
     </row>
@@ -401,7 +401,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="str">
-        <f aca="false">IF(AND(A4="Sales",B4=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A4="Sales",B4="General"),"Marketing",IF(A4="Sales","Sales","Marketing"))</f>
         <v>Marketing</v>
       </c>
     </row>
@@ -410,7 +410,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f aca="false">IF(AND(A5="Sales",B5=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A5="Sales",B5="General"),"Marketing",IF(A5="Sales","Sales","Marketing"))</f>
         <v>Marketing</v>
       </c>
     </row>
@@ -422,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f aca="false">IF(AND(A6="Sales",B6=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A6="Sales",B6="General"),"Marketing",IF(A6="Sales","Sales","Marketing"))</f>
         <v>Marketing</v>
       </c>
       <c r="D6" s="4"/>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="str">
-        <f aca="false">IF(AND(A7="Sales",B7=""),"Sales","Marketing")</f>
+        <f aca="false">IF(AND(A7="Sales",B7="General"),"Marketing",IF(A7="Sales","Sales","Marketing"))</f>
         <v>Sales</v>
       </c>
     </row>
